--- a/Survey_answer_key.xlsx
+++ b/Survey_answer_key.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fictional disease “Verrow fever”. If exposed: unvaccinated ~60/100 (SAR 60%); 1 dose ~27/100 (1st-dose efficacy 55%); 2 doses ~7/100 (2nd-dose efficacy 88%). Herd-immunity line ≈ 93%. All numbers hypothetical, not measles.</t>
+          <t>Fictional disease “Verrow fever”. If exposed: unvaccinated ~60/100 (SAR 60%); 1 dose ~27/100 (1st-dose efficacy 55%); 2 doses ~7/100 (2nd-dose efficacy 88%). Herd-immunity line ≈ 93%. All numbers hypothetical, not measles. Applies to all interface versions 1–30 — only the visualisation format differs; the underlying numbers and correct answers are identical across every version (baseline excepted).</t>
         </is>
       </c>
     </row>

--- a/Survey_answer_key.xlsx
+++ b/Survey_answer_key.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>4 cases — low vs others</t>
+          <t>20 cases — low vs others (~25th percentile; median 36)</t>
         </is>
       </c>
     </row>
